--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mapping du modèle métier Responsable/CDA/FHIR</t>
+    <t>Mapping Métier/CDA/FHIR : "Responsable du document"</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,9 +82,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce ConceptMap présente deux groupes de mapping : 
- - Groupe Mapping 1 : entre le modèle métier du responsable du document et l'élément CDA legalAuthenticator
- - Groupe Mapping 2 : entre l'élément CDA legalAuthenticator et l'élément FHIR Composition.attester</t>
+    <t xml:space="preserve">Ce ConceptMap présente deux groupes de mapping : 
+ - Mapping 1 : entre le modèle métier \"responsable\" et l'élément CDA \"legalAuthenticator\"
+ - Mapping 2 : entre l'élément CDA \"legalAuthenticator\" et l'élément FHIR \"Composition.attester\" </t>
   </si>
   <si>
     <t>Purpose</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingResponsableCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
